--- a/products/store_b/out/06_Savings_Goals_Sinking_Funds.xlsx
+++ b/products/store_b/out/06_Savings_Goals_Sinking_Funds.xlsx
@@ -859,11 +859,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="61622070"/>
-        <c:axId val="20711607"/>
+        <c:axId val="69718650"/>
+        <c:axId val="35062195"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61622070"/>
+        <c:axId val="69718650"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -895,7 +895,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20711607"/>
+        <c:crossAx val="35062195"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -903,7 +903,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20711607"/>
+        <c:axId val="35062195"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -945,7 +945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61622070"/>
+        <c:crossAx val="69718650"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
